--- a/Caracterizacion_Haces/data/z10mm-822.xlsx
+++ b/Caracterizacion_Haces/data/z10mm-822.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opticacuantica\Documents\Mateo Rubio\14-10-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opticacuantica\Documents\Mateo Rubio\15-10-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="165">
   <si>
     <t>*** BeamMaster USB Measurement system, Version 1.5.0.3 ***</t>
   </si>
@@ -128,400 +128,397 @@
     <t>0,0</t>
   </si>
   <si>
-    <t>-845,4</t>
-  </si>
-  <si>
-    <t>68,96</t>
-  </si>
-  <si>
-    <t>75,63</t>
-  </si>
-  <si>
-    <t>85,61</t>
-  </si>
-  <si>
-    <t>56,09</t>
-  </si>
-  <si>
-    <t>55,53</t>
-  </si>
-  <si>
-    <t>61,15</t>
+    <t>736,8</t>
+  </si>
+  <si>
+    <t>70,57</t>
+  </si>
+  <si>
+    <t>81,66</t>
+  </si>
+  <si>
+    <t>92,82</t>
+  </si>
+  <si>
+    <t>55,06</t>
+  </si>
+  <si>
+    <t>55,64</t>
+  </si>
+  <si>
+    <t>62,24</t>
   </si>
   <si>
     <t>0,2</t>
   </si>
   <si>
-    <t>-844,4</t>
-  </si>
-  <si>
-    <t>68,44</t>
-  </si>
-  <si>
-    <t>75,76</t>
-  </si>
-  <si>
-    <t>85,14</t>
-  </si>
-  <si>
-    <t>56,33</t>
-  </si>
-  <si>
-    <t>55,14</t>
-  </si>
-  <si>
-    <t>61,09</t>
+    <t>737,0</t>
+  </si>
+  <si>
+    <t>70,49</t>
+  </si>
+  <si>
+    <t>81,56</t>
+  </si>
+  <si>
+    <t>92,79</t>
+  </si>
+  <si>
+    <t>54,88</t>
+  </si>
+  <si>
+    <t>55,58</t>
+  </si>
+  <si>
+    <t>62,36</t>
   </si>
   <si>
     <t>0,4</t>
   </si>
   <si>
-    <t>68,97</t>
-  </si>
-  <si>
-    <t>75,54</t>
-  </si>
-  <si>
-    <t>85,30</t>
-  </si>
-  <si>
-    <t>56,46</t>
+    <t>70,74</t>
+  </si>
+  <si>
+    <t>81,70</t>
+  </si>
+  <si>
+    <t>93,26</t>
+  </si>
+  <si>
+    <t>54,60</t>
+  </si>
+  <si>
+    <t>55,29</t>
+  </si>
+  <si>
+    <t>62,07</t>
+  </si>
+  <si>
+    <t>0,6</t>
+  </si>
+  <si>
+    <t>81,68</t>
+  </si>
+  <si>
+    <t>92,83</t>
+  </si>
+  <si>
+    <t>55,31</t>
+  </si>
+  <si>
+    <t>55,42</t>
+  </si>
+  <si>
+    <t>62,06</t>
+  </si>
+  <si>
+    <t>0,8</t>
+  </si>
+  <si>
+    <t>738,4</t>
+  </si>
+  <si>
+    <t>70,64</t>
+  </si>
+  <si>
+    <t>81,42</t>
+  </si>
+  <si>
+    <t>92,73</t>
+  </si>
+  <si>
+    <t>54,95</t>
+  </si>
+  <si>
+    <t>55,47</t>
+  </si>
+  <si>
+    <t>61,88</t>
+  </si>
+  <si>
+    <t>1,0</t>
+  </si>
+  <si>
+    <t>735,9</t>
+  </si>
+  <si>
+    <t>70,62</t>
+  </si>
+  <si>
+    <t>81,33</t>
+  </si>
+  <si>
+    <t>92,85</t>
+  </si>
+  <si>
+    <t>54,59</t>
+  </si>
+  <si>
+    <t>55,48</t>
+  </si>
+  <si>
+    <t>61,92</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>737,6</t>
+  </si>
+  <si>
+    <t>70,75</t>
+  </si>
+  <si>
+    <t>81,34</t>
+  </si>
+  <si>
+    <t>92,86</t>
+  </si>
+  <si>
+    <t>54,76</t>
+  </si>
+  <si>
+    <t>55,70</t>
+  </si>
+  <si>
+    <t>61,91</t>
+  </si>
+  <si>
+    <t>1,4</t>
+  </si>
+  <si>
+    <t>70,56</t>
+  </si>
+  <si>
+    <t>81,69</t>
+  </si>
+  <si>
+    <t>92,92</t>
+  </si>
+  <si>
+    <t>55,35</t>
+  </si>
+  <si>
+    <t>61,98</t>
+  </si>
+  <si>
+    <t>1,6</t>
+  </si>
+  <si>
+    <t>736,2</t>
+  </si>
+  <si>
+    <t>70,61</t>
+  </si>
+  <si>
+    <t>81,76</t>
+  </si>
+  <si>
+    <t>93,09</t>
+  </si>
+  <si>
+    <t>54,82</t>
   </si>
   <si>
     <t>55,37</t>
   </si>
   <si>
-    <t>61,13</t>
-  </si>
-  <si>
-    <t>0,6</t>
-  </si>
-  <si>
-    <t>68,86</t>
-  </si>
-  <si>
-    <t>75,79</t>
-  </si>
-  <si>
-    <t>85,55</t>
-  </si>
-  <si>
-    <t>56,29</t>
-  </si>
-  <si>
-    <t>55,27</t>
-  </si>
-  <si>
-    <t>61,50</t>
-  </si>
-  <si>
-    <t>0,8</t>
-  </si>
-  <si>
-    <t>69,17</t>
-  </si>
-  <si>
-    <t>85,52</t>
-  </si>
-  <si>
-    <t>56,49</t>
+    <t>61,71</t>
+  </si>
+  <si>
+    <t>1,8</t>
+  </si>
+  <si>
+    <t>70,30</t>
+  </si>
+  <si>
+    <t>54,84</t>
+  </si>
+  <si>
+    <t>55,71</t>
+  </si>
+  <si>
+    <t>61,89</t>
+  </si>
+  <si>
+    <t>2,0</t>
+  </si>
+  <si>
+    <t>70,48</t>
+  </si>
+  <si>
+    <t>81,60</t>
+  </si>
+  <si>
+    <t>92,77</t>
+  </si>
+  <si>
+    <t>54,96</t>
+  </si>
+  <si>
+    <t>61,70</t>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>737,8</t>
+  </si>
+  <si>
+    <t>70,73</t>
+  </si>
+  <si>
+    <t>81,54</t>
+  </si>
+  <si>
+    <t>92,88</t>
+  </si>
+  <si>
+    <t>55,01</t>
+  </si>
+  <si>
+    <t>55,52</t>
+  </si>
+  <si>
+    <t>61,97</t>
+  </si>
+  <si>
+    <t>2,4</t>
+  </si>
+  <si>
+    <t>738,6</t>
+  </si>
+  <si>
+    <t>70,82</t>
+  </si>
+  <si>
+    <t>81,73</t>
   </si>
   <si>
     <t>55,33</t>
   </si>
   <si>
-    <t>60,79</t>
-  </si>
-  <si>
-    <t>1,0</t>
-  </si>
-  <si>
-    <t>-846,0</t>
-  </si>
-  <si>
-    <t>68,84</t>
-  </si>
-  <si>
-    <t>75,64</t>
-  </si>
-  <si>
-    <t>85,22</t>
-  </si>
-  <si>
-    <t>56,55</t>
-  </si>
-  <si>
-    <t>55,38</t>
-  </si>
-  <si>
-    <t>61,44</t>
-  </si>
-  <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>-845,2</t>
-  </si>
-  <si>
-    <t>69,42</t>
-  </si>
-  <si>
-    <t>85,83</t>
-  </si>
-  <si>
-    <t>56,31</t>
-  </si>
-  <si>
-    <t>55,03</t>
-  </si>
-  <si>
-    <t>61,20</t>
-  </si>
-  <si>
-    <t>1,4</t>
-  </si>
-  <si>
-    <t>-846,8</t>
-  </si>
-  <si>
-    <t>68,81</t>
-  </si>
-  <si>
-    <t>75,70</t>
-  </si>
-  <si>
-    <t>85,44</t>
-  </si>
-  <si>
-    <t>56,26</t>
-  </si>
-  <si>
-    <t>55,30</t>
-  </si>
-  <si>
-    <t>60,80</t>
-  </si>
-  <si>
-    <t>1,6</t>
-  </si>
-  <si>
-    <t>68,85</t>
-  </si>
-  <si>
-    <t>75,66</t>
-  </si>
-  <si>
-    <t>85,41</t>
-  </si>
-  <si>
-    <t>55,35</t>
-  </si>
-  <si>
-    <t>60,98</t>
-  </si>
-  <si>
-    <t>1,8</t>
-  </si>
-  <si>
-    <t>69,10</t>
-  </si>
-  <si>
-    <t>75,62</t>
-  </si>
-  <si>
-    <t>85,34</t>
-  </si>
-  <si>
-    <t>56,66</t>
+    <t>55,62</t>
+  </si>
+  <si>
+    <t>62,05</t>
+  </si>
+  <si>
+    <t>2,6</t>
+  </si>
+  <si>
+    <t>737,3</t>
+  </si>
+  <si>
+    <t>70,36</t>
+  </si>
+  <si>
+    <t>81,51</t>
+  </si>
+  <si>
+    <t>92,63</t>
+  </si>
+  <si>
+    <t>54,90</t>
+  </si>
+  <si>
+    <t>55,55</t>
+  </si>
+  <si>
+    <t>62,01</t>
+  </si>
+  <si>
+    <t>2,8</t>
+  </si>
+  <si>
+    <t>70,41</t>
+  </si>
+  <si>
+    <t>92,62</t>
+  </si>
+  <si>
+    <t>55,02</t>
+  </si>
+  <si>
+    <t>3,0</t>
+  </si>
+  <si>
+    <t>736,5</t>
+  </si>
+  <si>
+    <t>70,70</t>
+  </si>
+  <si>
+    <t>81,57</t>
+  </si>
+  <si>
+    <t>55,00</t>
+  </si>
+  <si>
+    <t>55,77</t>
+  </si>
+  <si>
+    <t>62,39</t>
+  </si>
+  <si>
+    <t>3,2</t>
+  </si>
+  <si>
+    <t>70,92</t>
+  </si>
+  <si>
+    <t>81,46</t>
+  </si>
+  <si>
+    <t>92,90</t>
+  </si>
+  <si>
+    <t>55,08</t>
+  </si>
+  <si>
+    <t>55,36</t>
+  </si>
+  <si>
+    <t>61,96</t>
+  </si>
+  <si>
+    <t>3,4</t>
+  </si>
+  <si>
+    <t>70,67</t>
+  </si>
+  <si>
+    <t>81,45</t>
+  </si>
+  <si>
+    <t>92,68</t>
+  </si>
+  <si>
+    <t>55,13</t>
+  </si>
+  <si>
+    <t>3,6</t>
+  </si>
+  <si>
+    <t>81,49</t>
+  </si>
+  <si>
+    <t>55,07</t>
+  </si>
+  <si>
+    <t>3,8</t>
+  </si>
+  <si>
+    <t>738,1</t>
+  </si>
+  <si>
+    <t>81,48</t>
+  </si>
+  <si>
+    <t>54,80</t>
   </si>
   <si>
     <t>55,43</t>
-  </si>
-  <si>
-    <t>61,06</t>
-  </si>
-  <si>
-    <t>2,0</t>
-  </si>
-  <si>
-    <t>-844,9</t>
-  </si>
-  <si>
-    <t>68,79</t>
-  </si>
-  <si>
-    <t>75,81</t>
-  </si>
-  <si>
-    <t>85,33</t>
-  </si>
-  <si>
-    <t>56,56</t>
-  </si>
-  <si>
-    <t>55,20</t>
-  </si>
-  <si>
-    <t>61,19</t>
-  </si>
-  <si>
-    <t>2,2</t>
-  </si>
-  <si>
-    <t>68,75</t>
-  </si>
-  <si>
-    <t>75,60</t>
-  </si>
-  <si>
-    <t>85,27</t>
-  </si>
-  <si>
-    <t>56,32</t>
-  </si>
-  <si>
-    <t>55,28</t>
-  </si>
-  <si>
-    <t>60,93</t>
-  </si>
-  <si>
-    <t>2,4</t>
-  </si>
-  <si>
-    <t>-844,6</t>
-  </si>
-  <si>
-    <t>68,83</t>
-  </si>
-  <si>
-    <t>75,65</t>
-  </si>
-  <si>
-    <t>85,35</t>
-  </si>
-  <si>
-    <t>56,36</t>
-  </si>
-  <si>
-    <t>55,05</t>
-  </si>
-  <si>
-    <t>61,10</t>
-  </si>
-  <si>
-    <t>2,6</t>
-  </si>
-  <si>
-    <t>69,00</t>
-  </si>
-  <si>
-    <t>75,83</t>
-  </si>
-  <si>
-    <t>85,47</t>
-  </si>
-  <si>
-    <t>56,61</t>
-  </si>
-  <si>
-    <t>55,24</t>
-  </si>
-  <si>
-    <t>61,11</t>
-  </si>
-  <si>
-    <t>2,8</t>
-  </si>
-  <si>
-    <t>68,67</t>
-  </si>
-  <si>
-    <t>75,77</t>
-  </si>
-  <si>
-    <t>55,93</t>
-  </si>
-  <si>
-    <t>55,54</t>
-  </si>
-  <si>
-    <t>3,0</t>
-  </si>
-  <si>
-    <t>-844,1</t>
-  </si>
-  <si>
-    <t>69,04</t>
-  </si>
-  <si>
-    <t>85,80</t>
-  </si>
-  <si>
-    <t>56,10</t>
-  </si>
-  <si>
-    <t>61,26</t>
-  </si>
-  <si>
-    <t>3,2</t>
-  </si>
-  <si>
-    <t>85,81</t>
-  </si>
-  <si>
-    <t>55,97</t>
-  </si>
-  <si>
-    <t>55,09</t>
-  </si>
-  <si>
-    <t>60,58</t>
-  </si>
-  <si>
-    <t>3,4</t>
-  </si>
-  <si>
-    <t>68,68</t>
-  </si>
-  <si>
-    <t>75,53</t>
-  </si>
-  <si>
-    <t>56,21</t>
-  </si>
-  <si>
-    <t>55,29</t>
-  </si>
-  <si>
-    <t>3,6</t>
-  </si>
-  <si>
-    <t>69,30</t>
-  </si>
-  <si>
-    <t>85,60</t>
-  </si>
-  <si>
-    <t>54,94</t>
-  </si>
-  <si>
-    <t>61,31</t>
-  </si>
-  <si>
-    <t>3,8</t>
-  </si>
-  <si>
-    <t>68,64</t>
-  </si>
-  <si>
-    <t>85,19</t>
-  </si>
-  <si>
-    <t>56,37</t>
-  </si>
-  <si>
-    <t>61,25</t>
   </si>
 </sst>
 </file>
@@ -862,7 +859,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -870,7 +867,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.59482638888888884</v>
+        <v>0.77236111111111105</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1011,7 +1008,7 @@
         <v>34</v>
       </c>
       <c r="C23">
-        <v>2639</v>
+        <v>1037</v>
       </c>
       <c r="D23" t="s">
         <v>35</v>
@@ -1040,7 +1037,7 @@
         <v>42</v>
       </c>
       <c r="C24">
-        <v>2639</v>
+        <v>1037</v>
       </c>
       <c r="D24" t="s">
         <v>43</v>
@@ -1066,10 +1063,10 @@
         <v>49</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C25">
-        <v>2639</v>
+        <v>1039</v>
       </c>
       <c r="D25" t="s">
         <v>50</v>
@@ -1098,135 +1095,135 @@
         <v>42</v>
       </c>
       <c r="C26">
-        <v>2640</v>
+        <v>1039</v>
       </c>
       <c r="D26" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" t="s">
         <v>57</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>58</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>59</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>60</v>
       </c>
-      <c r="H26" t="s">
+      <c r="I26" t="s">
         <v>61</v>
-      </c>
-      <c r="I26" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" t="s">
         <v>63</v>
       </c>
-      <c r="B27" t="s">
-        <v>34</v>
-      </c>
       <c r="C27">
-        <v>2638</v>
+        <v>1037</v>
       </c>
       <c r="D27" t="s">
         <v>64</v>
       </c>
       <c r="E27" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="F27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C28">
-        <v>2637</v>
+        <v>1036</v>
       </c>
       <c r="D28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G28" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I28" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C29">
-        <v>2638</v>
+        <v>1037</v>
       </c>
       <c r="D29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E29" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F29" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G29" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H29" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I29" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="C30">
-        <v>2637</v>
+        <v>1037</v>
       </c>
       <c r="D30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G30" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="H30" t="s">
         <v>90</v>
@@ -1240,48 +1237,48 @@
         <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C31">
-        <v>2638</v>
+        <v>1038</v>
       </c>
       <c r="D31" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E31" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F31" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G31" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="H31" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I31" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="C32">
-        <v>2639</v>
+        <v>1039</v>
       </c>
       <c r="D32" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E32" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="F32" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="G32" t="s">
         <v>102</v>
@@ -1298,289 +1295,289 @@
         <v>105</v>
       </c>
       <c r="B33" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33">
+        <v>1036</v>
+      </c>
+      <c r="D33" t="s">
         <v>106</v>
       </c>
-      <c r="C33">
-        <v>2638</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>107</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>108</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>109</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
+        <v>76</v>
+      </c>
+      <c r="I33" t="s">
         <v>110</v>
-      </c>
-      <c r="H33" t="s">
-        <v>111</v>
-      </c>
-      <c r="I33" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" t="s">
+        <v>112</v>
+      </c>
+      <c r="C34">
+        <v>1037</v>
+      </c>
+      <c r="D34" t="s">
         <v>113</v>
       </c>
-      <c r="B34" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34">
-        <v>2636</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>114</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>115</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>116</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>117</v>
       </c>
-      <c r="H34" t="s">
+      <c r="I34" t="s">
         <v>118</v>
-      </c>
-      <c r="I34" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>119</v>
+      </c>
+      <c r="B35" t="s">
         <v>120</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35">
+        <v>1040</v>
+      </c>
+      <c r="D35" t="s">
         <v>121</v>
       </c>
-      <c r="C35">
-        <v>2639</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>122</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
         <v>123</v>
       </c>
-      <c r="F35" t="s">
+      <c r="H35" t="s">
         <v>124</v>
       </c>
-      <c r="G35" t="s">
+      <c r="I35" t="s">
         <v>125</v>
-      </c>
-      <c r="H35" t="s">
-        <v>126</v>
-      </c>
-      <c r="I35" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" t="s">
+        <v>127</v>
+      </c>
+      <c r="C36">
+        <v>1038</v>
+      </c>
+      <c r="D36" t="s">
         <v>128</v>
       </c>
-      <c r="B36" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36">
-        <v>2638</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>129</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>130</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>131</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>132</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
         <v>133</v>
-      </c>
-      <c r="I36" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>134</v>
+      </c>
+      <c r="B37" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37">
+        <v>1040</v>
+      </c>
+      <c r="D37" t="s">
         <v>135</v>
       </c>
-      <c r="B37" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37">
-        <v>2636</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
+        <v>114</v>
+      </c>
+      <c r="F37" t="s">
         <v>136</v>
       </c>
-      <c r="E37" t="s">
+      <c r="G37" t="s">
         <v>137</v>
       </c>
-      <c r="F37" t="s">
-        <v>37</v>
-      </c>
-      <c r="G37" t="s">
-        <v>138</v>
-      </c>
       <c r="H37" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="I37" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>138</v>
+      </c>
+      <c r="B38" t="s">
+        <v>139</v>
+      </c>
+      <c r="C38">
+        <v>1038</v>
+      </c>
+      <c r="D38" t="s">
         <v>140</v>
       </c>
-      <c r="B38" t="s">
+      <c r="E38" t="s">
         <v>141</v>
       </c>
-      <c r="C38">
-        <v>2639</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
+        <v>115</v>
+      </c>
+      <c r="G38" t="s">
         <v>142</v>
       </c>
-      <c r="E38" t="s">
-        <v>137</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="H38" t="s">
         <v>143</v>
       </c>
-      <c r="G38" t="s">
+      <c r="I38" t="s">
         <v>144</v>
-      </c>
-      <c r="H38" t="s">
-        <v>96</v>
-      </c>
-      <c r="I38" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>145</v>
+      </c>
+      <c r="B39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39">
+        <v>1035</v>
+      </c>
+      <c r="D39" t="s">
         <v>146</v>
       </c>
-      <c r="B39" t="s">
-        <v>106</v>
-      </c>
-      <c r="C39">
-        <v>2637</v>
-      </c>
-      <c r="D39" t="s">
-        <v>35</v>
-      </c>
       <c r="E39" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="F39" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G39" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H39" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I39" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>152</v>
+      </c>
+      <c r="B40" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40">
+        <v>1039</v>
+      </c>
+      <c r="D40" t="s">
+        <v>153</v>
+      </c>
+      <c r="E40" t="s">
+        <v>154</v>
+      </c>
+      <c r="F40" t="s">
+        <v>155</v>
+      </c>
+      <c r="G40" t="s">
+        <v>156</v>
+      </c>
+      <c r="H40" t="s">
+        <v>39</v>
+      </c>
+      <c r="I40" t="s">
         <v>151</v>
-      </c>
-      <c r="B40" t="s">
-        <v>78</v>
-      </c>
-      <c r="C40">
-        <v>2638</v>
-      </c>
-      <c r="D40" t="s">
-        <v>152</v>
-      </c>
-      <c r="E40" t="s">
-        <v>153</v>
-      </c>
-      <c r="F40" t="s">
-        <v>73</v>
-      </c>
-      <c r="G40" t="s">
-        <v>154</v>
-      </c>
-      <c r="H40" t="s">
-        <v>155</v>
-      </c>
-      <c r="I40" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B41" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C41">
-        <v>2639</v>
+        <v>1035</v>
       </c>
       <c r="D41" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="E41" t="s">
-        <v>115</v>
+        <v>158</v>
       </c>
       <c r="F41" t="s">
-        <v>158</v>
+        <v>74</v>
       </c>
       <c r="G41" t="s">
-        <v>66</v>
+        <v>159</v>
       </c>
       <c r="H41" t="s">
-        <v>159</v>
+        <v>76</v>
       </c>
       <c r="I41" t="s">
-        <v>160</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>160</v>
+      </c>
+      <c r="B42" t="s">
         <v>161</v>
       </c>
-      <c r="B42" t="s">
-        <v>106</v>
-      </c>
       <c r="C42">
-        <v>2639</v>
+        <v>1038</v>
       </c>
       <c r="D42" t="s">
+        <v>87</v>
+      </c>
+      <c r="E42" t="s">
         <v>162</v>
       </c>
-      <c r="E42" t="s">
-        <v>94</v>
-      </c>
       <c r="F42" t="s">
+        <v>37</v>
+      </c>
+      <c r="G42" t="s">
         <v>163</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>164</v>
       </c>
-      <c r="H42" t="s">
-        <v>149</v>
-      </c>
       <c r="I42" t="s">
-        <v>165</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
